--- a/clean/mmycoides/building_data/automated-org-with-refs.xlsx
+++ b/clean/mmycoides/building_data/automated-org-with-refs.xlsx
@@ -6814,16 +6814,16 @@
     <t>Translation_termination_peptide_deformylase_processing</t>
   </si>
   <si>
+    <t>Transcription_stable_rho_dependent</t>
+  </si>
+  <si>
     <t>Transcription_stable_rho_independent</t>
   </si>
   <si>
-    <t>Transcription_stable_rho_dependent</t>
+    <t>Transcription_normal_rho_dependent</t>
   </si>
   <si>
     <t>Transcription_normal_rho_independent</t>
-  </si>
-  <si>
-    <t>Transcription_normal_rho_dependent</t>
   </si>
   <si>
     <t>Translation_initiation_gtp_factor_InfB</t>
